--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3311-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3311-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2441FBFF-5C4C-426D-926B-D15AEAE35422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CB0E64C-777B-4F77-9587-9F983ECEA7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6F5A06E3-0F39-4FAD-9E50-DD6B2C1D6688}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{9F2A9726-5EB1-4010-A02C-4F3396C1883E}"/>
   </bookViews>
   <sheets>
     <sheet name="3311-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1493,28 +1493,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D4DF72-DFAC-46A3-ACBA-E25076D645BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F47C6A-8A6C-4EC3-9CE5-E2C8A884ED06}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1584,7 +1584,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1704,7 +1704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>33</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>33</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>33</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2018</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2017</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2016</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2015</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2014</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2013</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2012</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2011</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2010</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2009</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2008</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2007</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2006</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2005</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2004</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2003</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36" t="s">
         <v>51</v>
       </c>
